--- a/data/gravel/Sklar PBJ 2025.xlsx
+++ b/data/gravel/Sklar PBJ 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4257536C-8EA5-5F48-B2E8-03E4577BB139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F10CFA-2211-0E48-BBD8-2D899F900104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32640" yWindow="-22240" windowWidth="26340" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8120" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -381,6 +381,9 @@
   </si>
   <si>
     <t>hardtail</t>
+  </si>
+  <si>
+    <t>https://sklarbikes.com/cdn/shop/files/sklar_PBJ_Steel_atb_chainstay_yoke_1.jpg?v=1759860155&amp;width=1296</t>
   </si>
 </sst>
 </file>
@@ -770,6 +773,11 @@
         <v>97</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>116</v>
+      </c>
+    </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>

--- a/data/gravel/Sklar PBJ 2025.xlsx
+++ b/data/gravel/Sklar PBJ 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F10CFA-2211-0E48-BBD8-2D899F900104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B19DCC-8120-4F45-B919-FEA4ABEE24E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8120" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="120">
   <si>
     <t>brand</t>
   </si>
@@ -384,6 +384,15 @@
   </si>
   <si>
     <t>https://sklarbikes.com/cdn/shop/files/sklar_PBJ_Steel_atb_chainstay_yoke_1.jpg?v=1759860155&amp;width=1296</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Oakland, California, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -727,7 +736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1720,6 +1729,17 @@
       <c r="A77" t="s">
         <v>84</v>
       </c>
+      <c r="B77" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>117</v>
+      </c>
+      <c r="B78" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/gravel/Sklar PBJ 2025.xlsx
+++ b/data/gravel/Sklar PBJ 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B19DCC-8120-4F45-B919-FEA4ABEE24E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C04662-0F40-BE40-A9B0-F96528AF75DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="126">
   <si>
     <t>brand</t>
   </si>
@@ -393,6 +393,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -736,7 +754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1564,180 +1582,210 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>62</v>
+        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56">
-        <v>31.6</v>
+        <v>122</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>64</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>65</v>
-      </c>
-      <c r="B58">
-        <v>36</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>66</v>
+        <v>125</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>67</v>
+        <v>61</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>68</v>
-      </c>
-      <c r="B61">
-        <v>160</v>
+        <v>62</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>69</v>
+        <v>63</v>
+      </c>
+      <c r="B62">
+        <v>31.6</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>71</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>113</v>
+        <v>65</v>
+      </c>
+      <c r="B64">
+        <v>36</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>75</v>
-      </c>
-      <c r="B68">
-        <v>1</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>78</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>79</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>80</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>85</v>
+        <v>74</v>
+      </c>
+      <c r="B73">
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B74">
-        <v>1599</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>82</v>
-      </c>
-      <c r="B75">
-        <v>4299</v>
+        <v>76</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>83</v>
+        <v>77</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>79</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>80</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>82</v>
+      </c>
+      <c r="B81">
+        <v>4299</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>84</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>117</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B84" t="s">
         <v>118</v>
       </c>
     </row>

--- a/data/gravel/Sklar PBJ 2025.xlsx
+++ b/data/gravel/Sklar PBJ 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C04662-0F40-BE40-A9B0-F96528AF75DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{384F3ACF-4676-044E-944C-11F41286BB14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7860" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -308,9 +308,6 @@
     <t>frame size</t>
   </si>
   <si>
-    <t>trail</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -353,12 +350,6 @@
     <t>max_dropper_insertion</t>
   </si>
   <si>
-    <t>rider_min_spec</t>
-  </si>
-  <si>
-    <t>rider_max_spec</t>
-  </si>
-  <si>
     <t>min saddle height</t>
   </si>
   <si>
@@ -377,9 +368,6 @@
     <t>internal</t>
   </si>
   <si>
-    <t>a8:g37</t>
-  </si>
-  <si>
     <t>hardtail</t>
   </si>
   <si>
@@ -411,15 +399,21 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>a8:g36</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
@@ -453,11 +447,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -754,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -773,7 +766,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -797,12 +790,12 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -810,7 +803,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -821,7 +814,7 @@
         <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
         <v>9</v>
@@ -956,7 +949,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C14">
         <v>317</v>
@@ -1025,7 +1018,7 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C17">
         <v>432</v>
@@ -1068,10 +1061,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -1117,7 +1110,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C21">
         <v>1098</v>
@@ -1206,10 +1199,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C25">
         <v>172</v>
@@ -1229,254 +1222,241 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>91</v>
+        <v>123</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31">
-        <v>700</v>
-      </c>
-      <c r="D31">
-        <v>700</v>
-      </c>
-      <c r="E31">
-        <v>700</v>
-      </c>
-      <c r="F31">
-        <v>700</v>
-      </c>
-      <c r="G31">
-        <v>700</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C32">
-        <v>66</v>
+        <v>700</v>
       </c>
       <c r="D32">
-        <v>66</v>
+        <v>700</v>
       </c>
       <c r="E32">
-        <v>66</v>
+        <v>700</v>
       </c>
       <c r="F32">
-        <v>66</v>
+        <v>700</v>
       </c>
       <c r="G32">
-        <v>66</v>
+        <v>700</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D33">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E33">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F33">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G33">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="3">
-        <f>C36</f>
-        <v>145.24578260869566</v>
-      </c>
-      <c r="D34" s="3">
-        <f>AVERAGE(D36,C37)</f>
-        <v>158.78534782608693</v>
-      </c>
-      <c r="E34" s="3">
-        <f t="shared" ref="E34:G34" si="0">AVERAGE(E36,D37)</f>
-        <v>167.4014347826087</v>
-      </c>
-      <c r="F34" s="3">
-        <f t="shared" si="0"/>
-        <v>180.94099999999997</v>
-      </c>
-      <c r="G34" s="3">
-        <f t="shared" si="0"/>
-        <v>193.2496956521739</v>
+        <v>45</v>
+      </c>
+      <c r="C34">
+        <v>71</v>
+      </c>
+      <c r="D34">
+        <v>71</v>
+      </c>
+      <c r="E34">
+        <v>71</v>
+      </c>
+      <c r="F34">
+        <v>71</v>
+      </c>
+      <c r="G34">
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35">
+        <f>(0.0146 + C37*1.1324)/0.46/10</f>
+        <v>145.24578260869566</v>
+      </c>
+      <c r="D35">
+        <f t="shared" ref="D35:G35" si="0">(0.0146 + D37*1.1324)/0.46/10</f>
+        <v>157.55447826086956</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="0"/>
+        <v>166.1705652173913</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="0"/>
+        <v>179.7101304347826</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="0"/>
+        <v>192.01882608695652</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>47</v>
-      </c>
-      <c r="B35" t="s">
-        <v>47</v>
-      </c>
-      <c r="C35" s="3">
-        <f>D34</f>
-        <v>158.78534782608693</v>
-      </c>
-      <c r="D35" s="3">
-        <f t="shared" ref="D35:F35" si="1">E34</f>
-        <v>167.4014347826087</v>
-      </c>
-      <c r="E35" s="3">
-        <f t="shared" si="1"/>
-        <v>180.94099999999997</v>
-      </c>
-      <c r="F35" s="3">
-        <f t="shared" si="1"/>
-        <v>193.2496956521739</v>
-      </c>
-      <c r="G35" s="3">
-        <f t="shared" ref="G35" si="2">G37</f>
-        <v>199.40404347826086</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C36">
         <f>(0.0146 + C38*1.1324)/0.46/10</f>
-        <v>145.24578260869566</v>
+        <v>160.01621739130434</v>
       </c>
       <c r="D36">
-        <f t="shared" ref="D36:G36" si="3">(0.0146 + D38*1.1324)/0.46/10</f>
-        <v>157.55447826086956</v>
+        <f t="shared" ref="D36:G36" si="1">(0.0146 + D38*1.1324)/0.46/10</f>
+        <v>168.63230434782608</v>
       </c>
       <c r="E36">
-        <f t="shared" si="3"/>
-        <v>166.1705652173913</v>
+        <f t="shared" si="1"/>
+        <v>182.17186956521738</v>
       </c>
       <c r="F36">
-        <f t="shared" si="3"/>
-        <v>179.7101304347826</v>
+        <f t="shared" si="1"/>
+        <v>194.4805652173913</v>
       </c>
       <c r="G36">
-        <f t="shared" si="3"/>
-        <v>192.01882608695652</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>110</v>
+        <f t="shared" si="1"/>
+        <v>199.40404347826086</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="C37">
-        <f>(0.0146 + C39*1.1324)/0.46/10</f>
-        <v>160.01621739130434</v>
+        <v>590</v>
       </c>
       <c r="D37">
-        <f t="shared" ref="D37:G37" si="4">(0.0146 + D39*1.1324)/0.46/10</f>
-        <v>168.63230434782608</v>
+        <v>640</v>
       </c>
       <c r="E37">
-        <f t="shared" si="4"/>
-        <v>182.17186956521738</v>
+        <v>675</v>
       </c>
       <c r="F37">
-        <f t="shared" si="4"/>
-        <v>194.4805652173913</v>
+        <v>730</v>
       </c>
       <c r="G37">
-        <f t="shared" si="4"/>
-        <v>199.40404347826086</v>
+        <v>780</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" t="s">
+        <v>49</v>
+      </c>
       <c r="C38">
-        <v>590</v>
+        <v>650</v>
       </c>
       <c r="D38">
-        <v>640</v>
+        <v>685</v>
       </c>
       <c r="E38">
-        <v>675</v>
+        <v>740</v>
       </c>
       <c r="F38">
-        <v>730</v>
+        <v>790</v>
       </c>
       <c r="G38">
-        <v>780</v>
+        <v>810</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>48</v>
-      </c>
-      <c r="B39" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39">
-        <v>650</v>
-      </c>
-      <c r="D39">
-        <v>685</v>
-      </c>
-      <c r="E39">
-        <v>740</v>
-      </c>
-      <c r="F39">
-        <v>790</v>
-      </c>
-      <c r="G39">
-        <v>810</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>109</v>
+        <v>91</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
@@ -1484,245 +1464,244 @@
         <v>92</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>93</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>111</v>
+      <c r="B41" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>94</v>
-      </c>
-      <c r="B42" t="s">
-        <v>95</v>
+        <v>50</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>85</v>
+        <v>52</v>
+      </c>
+      <c r="B44" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1">
-        <v>10</v>
+        <v>53</v>
+      </c>
+      <c r="B45">
+        <v>2.8</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46">
-        <f>2.8*25.4</f>
-        <v>71.11999999999999</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="B47">
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48">
-        <v>100</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="B51">
+        <v>148</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B52">
-        <v>148</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>125</v>
+        <v>61</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>61</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="B61">
+        <v>31.6</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>63</v>
-      </c>
-      <c r="B62">
-        <v>31.6</v>
+        <v>64</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>64</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>88</v>
+        <v>65</v>
+      </c>
+      <c r="B63">
+        <v>36</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>65</v>
-      </c>
-      <c r="B64">
-        <v>36</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="B66">
+        <v>160</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>68</v>
-      </c>
-      <c r="B67">
-        <v>160</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>71</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="B72">
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>75</v>
-      </c>
-      <c r="B74">
-        <v>1</v>
+        <v>76</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>85</v>
@@ -1730,7 +1709,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>85</v>
@@ -1738,7 +1717,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>85</v>
@@ -1746,47 +1725,39 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>80</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
+      </c>
+      <c r="B79">
+        <v>1599</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B80">
-        <v>1599</v>
+        <v>4299</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>82</v>
-      </c>
-      <c r="B81">
-        <v>4299</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>84</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>117</v>
-      </c>
-      <c r="B84" t="s">
-        <v>118</v>
+        <v>113</v>
+      </c>
+      <c r="B83" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
